--- a/Excel_files/TestDeliverables_Thejaswini_85010969.xlsx
+++ b/Excel_files/TestDeliverables_Thejaswini_85010969.xlsx
@@ -5,15 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ManualTestCaseStudies\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Testing_Bootcamp\Excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C9BE5B5-37B6-4119-BA0D-F1A970071B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67649DF7-F3BB-4434-BFAF-647514785D67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C918E590-609F-A84C-9DC0-8FBD3841576F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{C918E590-609F-A84C-9DC0-8FBD3841576F}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Scenarios" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="151">
   <si>
     <t>Scenario ID</t>
   </si>
@@ -419,13 +422,449 @@
   </si>
   <si>
     <t>Ticket is cancelled successfully, booking status is updated to Cancelled, and the applicable refund amount is displayed.</t>
+  </si>
+  <si>
+    <t>Project Name:</t>
+  </si>
+  <si>
+    <t>Railway Booking Application</t>
+  </si>
+  <si>
+    <t>Module Name:</t>
+  </si>
+  <si>
+    <t>Indian Railways</t>
+  </si>
+  <si>
+    <t>Date Updated:</t>
+  </si>
+  <si>
+    <t>29/08/2026</t>
+  </si>
+  <si>
+    <t>Last Build Tested:</t>
+  </si>
+  <si>
+    <t>Reviewed By:</t>
+  </si>
+  <si>
+    <t>Raghavendra BN</t>
+  </si>
+  <si>
+    <t>Run No:</t>
+  </si>
+  <si>
+    <t>10 Test Cases</t>
+  </si>
+  <si>
+    <t>Executed By:</t>
+  </si>
+  <si>
+    <t>Raghavendra BN and Thejaswini</t>
+  </si>
+  <si>
+    <t>Run Date:</t>
+  </si>
+  <si>
+    <t>Test Objectives:</t>
+  </si>
+  <si>
+    <t>Mapping Test Scenarios with Test Cases (Indian Railways )</t>
+  </si>
+  <si>
+    <t>Test Setup:</t>
+  </si>
+  <si>
+    <t>MS Excel Sheet 2026, Microsoft Edge browser</t>
+  </si>
+  <si>
+    <t>Req_Id</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Test_Case ID</t>
+  </si>
+  <si>
+    <t>Test_Case_Description</t>
+  </si>
+  <si>
+    <t>Test_steps</t>
+  </si>
+  <si>
+    <t>Test_Data</t>
+  </si>
+  <si>
+    <t>Expected_Result</t>
+  </si>
+  <si>
+    <t>Actual_Result</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Req_1.0</t>
+  </si>
+  <si>
+    <t>TC_01</t>
+  </si>
+  <si>
+    <t>Verify user should register with valid details</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. User should open Microsoft Edge Browser  
+2. User should navigate to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>https://www.indianrail.gov.in</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/  
+3. User should Enter</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Username</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in Edit Box/ Text Box                                                4 .User Should Enter </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Password</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in Edit Box                                                                5. User Should Click on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sign In/ Login</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Button</t>
+    </r>
+  </si>
+  <si>
+    <t>URL: https://www.indianrail.gov.in/
+Name: Test User
+Email: test@gmail.com
+Mobile: 9090909090
+Password: Test@1234</t>
+  </si>
+  <si>
+    <t>User account should be created successfully and user should be redirected to OTP page</t>
+  </si>
+  <si>
+    <t>User account created successfully</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>Req_1.1</t>
+  </si>
+  <si>
+    <t>TC_02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify user can login with valid credentials  </t>
+  </si>
+  <si>
+    <t>1. User should open Microsoft Edge browser  
+2. User should navigate to https://www.indianrail.gov.in/  
+3. User should click on “Account &amp; Lists” / “Sign In” option on the Amazon homepage  
+4. User should enter valid Email ID/Mobile Number and Password  
+5. User should click on Login button</t>
+  </si>
+  <si>
+    <t>URL: https://www.indianrail.gov.in/
+Mobile: 9090909090
+Password: Test@1234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User should be logged in successfully and Indian Railways homepage/account page should be displayed  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">User logged in successfully andIndian Railways homepage/account page is displayed </t>
+  </si>
+  <si>
+    <t>Req_1.2</t>
+  </si>
+  <si>
+    <t>TC_03</t>
+  </si>
+  <si>
+    <t>Verify user can search for trains</t>
+  </si>
+  <si>
+    <t>User should open Microsoft Edge browser.
+User should navigate to the Indian Railways website.
+User should enter source station.
+User should enter destination station.
+User should select the journey date.
+User should click on the Search button.</t>
+  </si>
+  <si>
+    <t>From: Hyderabad
+To: Vijayawada
+Journey Date: 15/09/2026</t>
+  </si>
+  <si>
+    <t>List of available trains between the selected source and destination should be displayed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Available trains are displayed successfully. </t>
+  </si>
+  <si>
+    <t>Req_1.3</t>
+  </si>
+  <si>
+    <t>TC_04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify user can view train details  </t>
+  </si>
+  <si>
+    <t>User should open Microsoft Edge browser.
+User should navigate to the Indian Railways website.
+User should search for trains.
+User should select a train from the search results.
+User should click on the Train Details option.</t>
+  </si>
+  <si>
+    <t>From: Hyderabad
+To: Vijayawada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selected train details such as train number, train name, departure time, arrival time and route should be displayed. </t>
+  </si>
+  <si>
+    <t>Train details are displayed successfully.</t>
+  </si>
+  <si>
+    <t>Req_1.4</t>
+  </si>
+  <si>
+    <t>TC_05</t>
+  </si>
+  <si>
+    <t>Verify user can check seat availability</t>
+  </si>
+  <si>
+    <t>User should open Microsoft Edge browser.
+User should navigate to the Indian Railways website.
+User should search for trains.
+User should select a train.
+User should select the required class.
+User should check seat availability.</t>
+  </si>
+  <si>
+    <t>From: Hyderabad
+To: Vijayawada
+Class: Sleeper</t>
+  </si>
+  <si>
+    <t>Availability status for the selected train and class should be displayed.</t>
+  </si>
+  <si>
+    <t>Seat availability is displayed successfully.</t>
+  </si>
+  <si>
+    <t>Req_1.5</t>
+  </si>
+  <si>
+    <t>TC_06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify user can book a train ticket successfully  </t>
+  </si>
+  <si>
+    <t>User should open Microsoft Edge browser.
+User should navigate to the Indian Railways website.
+User should search for the required train.
+User should select the train and class.
+User should enter valid passenger details.
+User should proceed to payment.
+User should complete the payment.</t>
+  </si>
+  <si>
+    <t>Passenger Name: Test User
+Age: 21
+Gender: Female
+Class: Sleeper</t>
+  </si>
+  <si>
+    <t>Ticket should be booked successfully and booking/PNR details should be displayed.</t>
+  </si>
+  <si>
+    <t>Ticket booked successfully and booking details are displayed.
+Status: Passed</t>
+  </si>
+  <si>
+    <t>Req_1.6</t>
+  </si>
+  <si>
+    <t>TC_07</t>
+  </si>
+  <si>
+    <t>Verify user can complete payment successfully</t>
+  </si>
+  <si>
+    <t>User should search and select a train.
+User should enter valid passenger details.
+User should proceed to payment.
+User should select a payment method.
+User should enter valid payment details.
+User should click on Pay/Submit.</t>
+  </si>
+  <si>
+    <t>Payment Method: UPI
+UPI ID: test@upi</t>
+  </si>
+  <si>
+    <t>Payment should be completed successfully and booking confirmation should be displayed.</t>
+  </si>
+  <si>
+    <t>Payment completed successfully.</t>
+  </si>
+  <si>
+    <t>Req_1.7</t>
+  </si>
+  <si>
+    <t>TC_08</t>
+  </si>
+  <si>
+    <t>Verify user can view booking history</t>
+  </si>
+  <si>
+    <t>User should open Microsoft Edge browser.
+User should login to the Indian Railways website.
+User should navigate to the Booking History/My Bookings section.
+User should select a previous booking.</t>
+  </si>
+  <si>
+    <t>URL: https://www.indianrail.gov.in/
+Booking Status: Confirmed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User should be able to view previous booking details including PNR, train details, journey date and booking status.
+</t>
+  </si>
+  <si>
+    <t>Booking history is displayed successfully.</t>
+  </si>
+  <si>
+    <t>Req_1.8</t>
+  </si>
+  <si>
+    <t>TC_09</t>
+  </si>
+  <si>
+    <t>Verify user can cancel a booked train ticket</t>
+  </si>
+  <si>
+    <t>User should login to the Indian Railways website.
+User should navigate to Booking History/My Bookings.
+User should select a confirmed ticket.
+User should click on the Cancel Ticket option.
+User should confirm the cancellation.</t>
+  </si>
+  <si>
+    <t>Booking Status: Confirmed
+PNR: 1234567890</t>
+  </si>
+  <si>
+    <t>Ticket should be cancelled successfully and the cancellation/refund details should be displayed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ticket cancelled successfully and cancellation details are displayed.
+</t>
+  </si>
+  <si>
+    <t>TC_10</t>
+  </si>
+  <si>
+    <t>Verify user can logout successfully</t>
+  </si>
+  <si>
+    <t>User should open Microsoft Edge browser.
+User should login to the Indian Railways website.
+User should click on the Profile/Account option.
+User should click on the Logout option.</t>
+  </si>
+  <si>
+    <t>URL: https://www.indianrail.gov.in/
+Valid User Credentials</t>
+  </si>
+  <si>
+    <t>User should be logged out successfully and redirected to the login/home page.</t>
+  </si>
+  <si>
+    <t>User logged out successfully.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -485,8 +924,36 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -499,8 +966,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -560,11 +1033,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -598,6 +1086,60 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1113,4 +1655,408 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B236C53-628B-4B7C-BF28-8268A6F45004}">
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.5" customWidth="1"/>
+    <col min="2" max="2" width="20.9140625" customWidth="1"/>
+    <col min="3" max="3" width="15.75" customWidth="1"/>
+    <col min="4" max="4" width="38.75" customWidth="1"/>
+    <col min="5" max="5" width="37.6640625" customWidth="1"/>
+    <col min="6" max="6" width="34.5" customWidth="1"/>
+    <col min="7" max="7" width="21.58203125" customWidth="1"/>
+    <col min="8" max="8" width="18.58203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="58" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="14"/>
+      <c r="D1" s="13"/>
+    </row>
+    <row r="2" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A3" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="13"/>
+      <c r="C3" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="14"/>
+      <c r="D5" s="13"/>
+    </row>
+    <row r="6" spans="1:8" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="13"/>
+    </row>
+    <row r="7" spans="1:8" ht="87" x14ac:dyDescent="0.35">
+      <c r="A7" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+    </row>
+    <row r="8" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="G8" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="H8" s="18" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="230.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="E9" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="F9" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="H9" s="24" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="223" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="H10" s="25" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="F11" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="H11" s="25" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="227" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="H12" s="25" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="226.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="H13" s="25" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="268.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="E14" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="H14" s="25" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="223" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="H15" s="25" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="201.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="G16" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="H16" s="25" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="207" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="E17" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="F17" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="G17" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="H17" s="29" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="179" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>146</v>
+      </c>
+      <c r="D18" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="E18" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="F18" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="G18" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="H18" s="29" t="s">
+        <v>88</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{049DE9AC-737B-4EEC-A2D0-18E7C23D224E}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6445CF55-41F7-4B6D-A6F1-8164C00DD6BE}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>